--- a/data_extactor/batch_10_fa/batch_0031_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0031_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | سخنوری | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نظارت | نوشتن | یادگیری فعال</t>
+          <t>ریاضیات | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | بیان شفاهی | توانایی عددی | استدلال قیاسی | درک شفاهی | درک نوشتاری | استدلال استقرایی | وضوح گفتار | بیان نوشتاری | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | حساسیت به مسئله | خلاقیت | روانی ایده‌ها | حافظه | انعطاف‌پذیری دسته‌بندی</t>
+          <t>استدلال ریاضی | بیان شفاهی | توانایی عددی | استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | بیان کتبی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | اصالت | روانی ایده‌ها | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | سخنرانی عمومی | آزادی در تصمیم‌گیری | ارتباط با دیگران | اهمیت دقت یا صحت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | آزادی در تصمیم‌گیری | ارتباط با دیگران | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان شیمی، پس از متوسطه | مدرسان علوم رایانه، پس از متوسطه | مدرسان اقتصاد، پس از متوسطه | مدرسان آموزش، پس از متوسطه | معلمان دوره ابتدایی، به جز آموزش ویژه | مدرسان جغرافیا، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، پس از متوسطه | معلمان دوره متوسطه اول، به جز آموزش ویژه و شغلی/فنی | مدرسان فیزیک، پس از متوسطه | مدرسان روان‌شناسی، پس از متوسطه | معلمان دوره متوسطه دوم، به جز آموزش ویژه و شغلی/فنی | مدرسان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دوره ابتدایی | دستیاران آموزشی، پس از متوسطه | مدرسان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان شیمی، پس از متوسطه | اساتید علوم رایانه، پس از متوسطه | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | استادان جغرافیا، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مدرسان فیزیک، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk 3D Studio Design | Autodesk 3ds Max | Autodesk AutoCAD | Autodesk Ecotect Analysis | Autodesk Inventor | Autodesk Mudbox | Autodesk Revit | Blackboard Learn | Blender | نرم‌افزار ویرایش مشارکتی | نرم‌افزار طراحی و نقشه‌کشی به کمک رایانه CADD | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | McNeel Rhinoceros 3D | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | نرم‌افزار Salesforce | نرم‌افزار مدل‌سازی سه‌بعدی | Trimble SketchUp Pro | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk 3D Studio Design | Autodesk 3ds Max | Autodesk AutoCAD | Autodesk Ecotect Analysis | Autodesk Inventor | Autodesk Mudbox | Autodesk Revit | Blackboard Learn | Blender | نرم‌افزار ویرایش مشارکتی | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | McNeel Rhinoceros 3D | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | نرم‌افزار Salesforce | نرم‌افزار مدل‌سازی سه‌بعدی | Trimble SketchUp Pro | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | راهبردهای یادگیری | نوشتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>طراحی | زبان انگلیسی | ساختمان و ساخت‌وساز | آموزش و پرورش | ارتباطات و رسانه | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای زیبا | مهندسی و فناوری | قانون و دولت | جامعه‌شناسی و مردم‌شناسی | ریاضیات | تاریخ و باستان‌شناسی | روان‌شناسی</t>
+          <t>طراحی | زبان انگلیسی | ساختمان و ساخت‌وساز | آموزش و پرورش | ارتباطات و رسانه | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای زیبا | مهندسی و فناوری | قانون و دولت | جامعه‌شناسی و انسان‌شناسی | ریاضیات | تاریخ و باستان‌شناسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | استدلال قیاسی | درک شفاهی | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | تجسم | خلاقیت | دید دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی</t>
+          <t>بیان شفاهی | وضوح گفتار | استدلال قیاسی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | تجسم | اصالت | بینایی دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | سخنرانی عمومی | ارتباط با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | مجاورت فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقت یا صحت | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | معماران، به جز معماران منظر و دریایی | مدرسان هنر، نمایش و موسیقی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه دوم | مدرسان علوم رایانه، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | مدرسان زبان و ادبیات انگلیسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | مدرسان جغرافیا، پس از متوسطه | هماهنگ‌کنندگان آموزشی | معماران منظر | مدرسان علوم کتابداری، پس از متوسطه | معلمان دوره متوسطه اول، به جز آموزش ویژه و شغلی/فنی | معلمان دوره متوسطه دوم، به جز آموزش ویژه و شغلی/فنی | دستیاران آموزشی، پس از متوسطه</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | معماران، به‌جز منظر و دریایی | مدرسان هنر، نمایش و موسیقی، آموزش عالی | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | اساتید علوم رایانه، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | مدرسان علوم محیطی، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | استادان جغرافیا، پس از متوسطه | هماهنگ‌کنندگان آموزشی | معماران منظر | مدرسان علوم کتابداری، آموزش عالی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخنوری | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | ریاضیات | تفکر انتقادی | نوشتن | یادگیری فعال | علوم | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | ریاضیات | تفکر انتقادی | نگارش | یادگیری فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | مکانیک | شیمی | مدیریت و اداره | تولید و پردازش</t>
+          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | مکانیک | شیمی | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک نوشتاری | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید نزدیک | حساسیت به مسئله | توانایی عددی | روانی ایده‌ها | خلاقیت | تجسم | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | وضوح گفتار | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی نزدیک | حساسیت به مسئله | توانایی عددی | روانی ایده‌ها | اصالت | تجسم | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | ارتباط با دیگران | سطح رقابت | سخنرانی عمومی | صرف زمان برای نشستن | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | اهمیت دقت یا صحت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | سطح رقابت | سخنرانی عمومی | صرف زمان برای نشستن | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مدرسان معماری، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مهندسان زیستی و مهندسان زیست‌پزشکی | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه دوم | مدرسان شیمی، پس از متوسطه | مدرسان علوم رایانه، پس از متوسطه | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | مدرسان علوم محیطی، پس از متوسطه | تکنسین‌ها و متخصصان مهندسی صنایع | مهندسان صنایع | مهندسان مواد | دانشمندان مواد | مدرسان علوم ریاضی، پس از متوسطه | تکنسین‌ها و متخصصان مهندسی مکانیک | مهندسان مکاترونیک | تکنسین‌ها و متخصصان مهندسی نانوتکنولوژی | مدرسان فیزیک، پس از متوسطه</t>
+          <t>مدیران معماری و مهندسی | مدرسان معماری، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مهندسان زیستی و مهندسان زیست‌پزشکی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان شیمی، پس از متوسطه | اساتید علوم رایانه، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مدرسان علوم محیطی، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان مواد | دانشمندان مواد | مدرسان علوم ریاضی، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدرسان فیزیک، پس از متوسطه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نوشتن | گوش دادن فعال | نظارت | علوم | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | وضوح گفتار | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | روانی ایده‌ها | دید نزدیک | نظم‌دهی اطلاعات | خلاقیت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | حافظه</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | روانی ایده‌ها | بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقت یا صحت | سطح رقابت | مکالمات تلفنی | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن | سطح رقابت | مکالمات تلفنی | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه دوم | مدرسان شیمی، پس از متوسطه | مدرسان اقتصاد، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم خانواده و مصرف‌کننده، پس از متوسطه | مربیان مدیریت مزرعه و خانه | کشاورزان، دامداران و سایر مدیران کشاورزی | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | مدرسان تخصص‌های بهداشتی، پس از متوسطه | مدیران علوم طبیعی | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | دانشمندان خاک و گیاه</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان شیمی، پس از متوسطه | استادان اقتصاد، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مربیان مدیریت مزرعه و خانه | کشاورزان، دامداران و سایر مدیران کشاورزی | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | مدیران علوم طبیعی | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aipotu | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | سیستم‌های اطلاعات جغرافیایی GIS | Google Docs | نرم‌افزار ایجاد گرافیک | IBM SPSS Statistics | نرم‌افزار تحلیل تصویر | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار مدل‌سازی | Moodle | National Instruments LabVIEW | PLOS Computational Biology | SAS | Sakai CLE | تجهیزات تحلیل فشار صوت | نرم‌افزار آماری | The Gene Explorer | The MathWorks MATLAB | The Mathworks SimBiology | The Protein Investigator | The Virtual Genetics Lab | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Aipotu | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Docs | نرم‌افزار ایجاد گرافیک | IBM SPSS Statistics | نرم‌افزار تحلیل تصویر | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار مدل‌سازی | Moodle | National Instruments LabVIEW | PLOS Computational Biology | SAS | Sakai CLE | تجهیزات تحلیل فشار صوت | نرم‌افزار آماری | The Gene Explorer | The MathWorks MATLAB | The Mathworks SimBiology | The Protein Investigator | The Virtual Genetics Lab | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخنوری | راهبردهای یادگیری | یادگیری فعال | علوم | نوشتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | ریاضیات</t>
+          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | علوم | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی | آموزش و پرورش | رایانه و الکترونیک | اداری | پزشکی و دندانپزشکی | ارتباطات و رسانه | جغرافیا</t>
+          <t>زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی | آموزش و پرورش | رایانه و الکترونیک | اداری | پزشکی و دندان‌پزشکی | ارتباطات و رسانه | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | بیان نوشتاری | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | نظم‌دهی اطلاعات | روانی ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | خلاقیت | دید دور</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | اصالت | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقت یا صحت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | مکالمات تلفنی | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | مکالمات تلفنی | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | زیست‌شناسان | مدرسان شیمی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | متخصصان ژنتیک | مدرسان جغرافیا، پس از متوسطه | مدرسان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | زیست‌شناسان مولکولی و سلولی | مدرسان فیزیک، پس از متوسطه | مدرسان روان‌شناسی، پس از متوسطه | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، پس از متوسطه | مدرسان خصوصی</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | زیست‌شناسان | مدرسان شیمی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | ژنتیک‌دان‌ها | استادان جغرافیا، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | زیست‌شناسان مولکولی و سلولی | مدرسان فیزیک، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apache Struts | Atlassian JIRA | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ESRI ArcGIS | نرم‌افزار تبادل الکترونیکی داده EDI | نرم‌افزار ایمیل | سیستم‌های اطلاعات جغرافیایی GIS | Google Angular | Google Docs | Hibernate ORM | نرم‌افزار اسکن تصویر | JavaScript | سیستم مدیریت یادگیری LMS | Leica Geosystems ERDAS IMAGINE | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | MySQL | Oracle Database | Oracle Java | Oracle WebLogic Server | نرم‌افزار SAP | SAS | Sakai CLE | نرم‌افزار Salesforce | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Apache Struts | Atlassian JIRA | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ESRI ArcGIS | نرم‌افزار تبادل الکترونیکی داده EDI | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Angular | Google Docs | Hibernate ORM | نرم‌افزار اسکن تصویر | JavaScript | سیستم مدیریت یادگیری LMS | Leica Geosystems ERDAS IMAGINE | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | MySQL | Oracle Database | Oracle Java | Oracle WebLogic Server | نرم‌افزار SAP | SAS | Sakai CLE | نرم‌افزار Salesforce | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | درک مطلب | نوشتن | سخنوری | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
+          <t>راهبردهای یادگیری | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | بیان نوشتاری | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | روانی ایده‌ها | خلاقیت</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سلامت و ایمنی سایر کارکنان | اهمیت دقت یا صحت | فراوانی تصمیم‌گیری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان آموزش شغلی/فنی، پس از متوسطه | مدرسان شیمی، پس از متوسطه | دانشمندان حفاظت | مدرسان اقتصاد، پس از متوسطه | مدرسان آموزش، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان جغرافیا، پس از متوسطه | مدرسان تخصص‌های بهداشتی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم ریاضی، پس از متوسطه | مدیران علوم طبیعی | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، پس از متوسطه</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | مدرسان شیمی، پس از متوسطه | دانشمندان حفاظت | استادان اقتصاد، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | مدرسان علوم محیطی، پس از متوسطه | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم ریاضی، پس از متوسطه | مدیران علوم طبیعی | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخنوری | درک مطلب | تفکر انتقادی | علوم | نوشتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | استدلال استقرایی | درک شفاهی | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | استدلال ریاضی | نظم‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها | حافظه</t>
+          <t>بیان شفاهی | وضوح گفتار | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال ریاضی | ترتیب‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | حفظ کردن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | ارتباط با دیگران | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقت یا صحت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان شیمی، پس از متوسطه | مدرسان علوم رایانه، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | مدرسان جغرافیا، پس از متوسطه | مدرسان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | مدیران علوم طبیعی | مدرسان فیزیک، پس از متوسطه | مدرسان روان‌شناسی، پس از متوسطه | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | معلمان دوره متوسطه دوم، به جز آموزش ویژه و شغلی/فنی | مدرسان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، پس از متوسطه | مدرسان خصوصی</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدرسان شیمی، پس از متوسطه | اساتید علوم رایانه، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | مدیران علوم طبیعی | مدرسان فیزیک، پس از متوسطه | استادان روان‌شناسی، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | استادان جامعه‌شناسی، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | نوشتن | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | درک شفاهی | درک نوشتاری | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها | انعطاف‌پذیری بستار | حافظه | استدلال ریاضی | خلاقیت</t>
+          <t>بیان شفاهی | بیان کتبی | درک شفاهی | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها | انعطاف‌پذیری بستار | حفظ کردن | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | سخنرانی عمومی | اهمیت دقت یا صحت | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج و خروجی‌های کاری سایر کارکنان | صرف زمان برای نشستن | سطح رقابت | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای نشستن | سطح رقابت | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | مدرسان علوم زیستی، پس از متوسطه | تکنسین‌های زیستی | معلمان آموزش شغلی/فنی، دوره متوسطه اول | تکنسین‌های شیمی | شیمی‌دانان | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | مدرسان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | زیست‌شناسان مولکولی و سلولی | مدیران علوم طبیعی | مدرسان فیزیک، پس از متوسطه | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، پس از متوسطه | مدرسان خصوصی</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | مدرسان علوم زیستی، پس از متوسطه | تکنسین‌های زیستی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | تکنسین‌های شیمی | شیمی‌دانان | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | زیست‌شناسان مولکولی و سلولی | مدیران علوم طبیعی | مدرسان فیزیک، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Autodesk AutoCAD | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ESRI ArcGIS | نرم‌افزار ایمیل | سیستم‌های اطلاعات جغرافیایی GIS | Google Docs | Google Drive | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Acrobat | Autodesk AutoCAD | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ESRI ArcGIS | نرم‌افزار ایمیل | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google Docs | Google Drive | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Sakai CLE | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | تفکر انتقادی | علوم | نوشتن | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | وضوح گفتار | درک شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | خلاقیت | روانی ایده‌ها | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک کتبی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقت یا صحت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | صرف زمان برای نشستن | فشار زمانی | نتایج و خروجی‌های کاری سایر کارکنان</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | سخنرانی عمومی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | صرف زمان برای نشستن | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان آموزش شغلی/فنی، پس از متوسطه | مدرسان شیمی، پس از متوسطه | دانشمندان حفاظت | مدرسان اقتصاد، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مدرسان علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | مدرسان جغرافیا، پس از متوسطه | مدرسان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | مدیران علوم طبیعی | مدرسان فیزیک، پس از متوسطه | مدرسان مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، پس از متوسطه</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | مدرسان شیمی، پس از متوسطه | دانشمندان حفاظت | استادان اقتصاد، پس از متوسطه | مدرسان مهندسی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | استادان جغرافیا، پس از متوسطه | استادان تخصص‌های بهداشتی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | مدیران علوم طبیعی | مدرسان فیزیک، پس از متوسطه | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | دستیاران آموزشی، مقطع پس از متوسطه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Blackboard Learn | C | C++ | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Edmodo | نرم‌افزار ایمیل | FFTPACK | FFTW | مترجم فرمول FORTRAN | GIPSY-OASIS | GNU Octave | Geant4 | Gnuplot | Google Docs | نرم‌افزار گرانش | نرم‌افزار اسکن تصویر | LAPACK | LaTeX | سیستم مدیریت یادگیری LMS | Maplesoft Maple | Mathsoft Mathcad | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | OriginLab Origin | PLplot | Pascal | Perl | Sakai CLE | Synergy Software KaleidaGraph | The MathWorks MATLAB | VASP Data Viewer | Visual Molecular Dynamics VMD | نرم‌افزار مرورگر وب | Wolfram Research Mathematica | iParadigms Turnitin | plotutils</t>
+          <t>Autodesk AutoCAD | Blackboard Learn | C | C++ | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | Edmodo | نرم‌افزار ایمیل | FFTPACK | FFTW | Formula translation/translator FORTRAN | GIPSY-OASIS | GNU Octave | Geant4 | Gnuplot | Google Docs | نرم‌افزار گرانش | نرم‌افزار اسکن تصویر | LAPACK | LaTeX | سیستم مدیریت یادگیری LMS | Maplesoft Maple | Mathsoft Mathcad | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | OriginLab Origin | PLplot | Pascal | Perl | Sakai CLE | Synergy Software KaleidaGraph | The MathWorks MATLAB | VASP Data Viewer | Visual Molecular Dynamics VMD | نرم‌افزار مرورگر وب | Wolfram Research Mathematica | iParadigms Turnitin | plotutils</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | علوم | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نوشتن | گوش دادن فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | سخن گفتن | علوم | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | وضوح گفتار | دید نزدیک | تشخیص گفتار | توانایی عددی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | خلاقیت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | توانایی عددی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | ارتباط با دیگران | سخنرانی عمومی | برخورد با مشتریان خارجی یا عموم مردم | فشار زمانی | اهمیت دقت یا صحت | مکالمات تلفنی</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | سخنرانی عمومی | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | اهمیت دقیق یا درست بودن | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ستاره‌شناسان | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه اول | مدرسان آموزش شغلی/فنی، پس از متوسطه | مدرسان شیمی، پس از متوسطه | مدرسان علوم رایانه، پس از متوسطه | دانشمندان پژوهشی رایانه و اطلاعات | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | ریاضی‌دانان | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم‌ها | تکنسین‌ها و متخصصان مهندسی نانوتکنولوژی | فیزیک‌دانان | دستیاران آموزشی، پس از متوسطه | مدرسان خصوصی</t>
+          <t>اخترشناسان | مدرسان علوم جوی، زمین، دریایی و فضایی، پس از متوسطه | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | مدرسان شیمی، پس از متوسطه | اساتید علوم رایانه، پس از متوسطه | دانشمندان تحقیقات کامپیوتر و اطلاعات | مدرسان مهندسی، پس از متوسطه | مدرسان علوم محیطی، پس از متوسطه | مدرسان علوم ریاضی، پس از متوسطه | ریاضی‌دانان | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | فیزیکدانان | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0031_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0031_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | استراتژی‌های یادگیری | نظارت | نگارش | یادگیری فعال</t>
+          <t>ریاضیات | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>ریاضیات | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | بیان شفاهی | محاسبات عددی | استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | بیان کتبی | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | ابتکار | روانی ایده‌ها | حافظه و به‌خاطرسپاری | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>استدلال ریاضی | بیان شفاهی | توانایی عددی | استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | بیان کتبی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | اصالت | روانی ایده‌ها | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه، متوسطه و زبان انگلیسی به بزرگسالان | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | استادان علوم زیستی در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان شیمی در دانشگاه‌ها | استادان علوم کامپیوتر در دانشگاه‌ها | استادان اقتصاد در دانشگاه‌ها | استادان علوم تربیتی در دانشگاه‌ها | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان جغرافیا در دانشگاه‌ها | کارشناسان برنامه‌ریزی آموزشی | استادان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها | دبیران دوره اول متوسطه، به‌جز آموزش استثنایی و فنی و حرفه‌ای | استادان فیزیک در دانشگاه‌ها | استادان روان‌شناسی در دانشگاه‌ها | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی و حرفه‌ای | استادان جامعه‌شناسی در دانشگاه‌ها | آموزگاران استثنایی دوره ابتدایی | دستیاران آموزشی در دانشگاه‌ها | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | استادان جغرافیای دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | استراتژی‌های یادگیری | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>طراحی | زبان انگلیسی | ساختمان و سازه | آموزش و تدریس | ارتباطات و رسانه | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای تجسمی | مهندسی و فناوری | حقوق و مقررات دولتی | جامعه‌شناسی و مردم‌شناسی | ریاضیات | تاریخ و باستان‌شناسی | روان‌شناسی</t>
+          <t>طراحی | زبان انگلیسی | ساختمان و ساخت‌وساز | آموزش و پرورش | ارتباطات و رسانه | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای زیبا | مهندسی و فناوری | قانون و دولت | جامعه‌شناسی و انسان‌شناسی | ریاضیات | تاریخ و باستان‌شناسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | استدلال قیاسی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | تجسم فضایی | ابتکار | دید دور | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری در ادراک الگوها | محاسبات عددی</t>
+          <t>بیان شفاهی | وضوح گفتار | استدلال قیاسی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | تجسم | اصالت | بینایی دور | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>استادان مردم‌شناسی و باستان‌شناسی در دانشگاه‌ها | مهندسان معمار، به‌جز معماران منظر و مهندسان سازه‌های دریایی | استادان هنر، نمایش و موسیقی در دانشگاه‌ها | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | استادان علوم کامپیوتر در دانشگاه‌ها | استادان مهندسی در دانشگاه‌ها | استادان زبان و ادبیات انگلیسی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان علوم خانواده و مدیریت مصرف در دانشگاه‌ها | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | کارشناسان برنامه‌ریزی آموزشی | مهندسان معماری منظر | استادان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها | دبیران دوره اول متوسطه، به‌جز آموزش استثنایی و فنی و حرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی و حرفه‌ای | دستیاران آموزشی در دانشگاه‌ها</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | استادان علوم رایانه، آموزش عالی | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مهندسان معمار منظر | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | استراتژی‌های یادگیری | شنیدن فعال | درک مطلب | ریاضیات | تفکر انتقادی | نگارش | یادگیری فعال | مهارت‌های علمی | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | ریاضیات | تفکر انتقادی | نگارش | یادگیری فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | آموزش و تدریس | مکانیک | شیمی | مدیریت و امور اداری | تولید و فرآوری</t>
+          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | مکانیک | شیمی | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی | دید نزدیک | حساسیت به مسئله | محاسبات عددی | روانی ایده‌ها | ابتکار | تجسم فضایی | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>بیان شفاهی | وضوح گفتار | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی نزدیک | حساسیت به مسئله | توانایی عددی | روانی ایده‌ها | اصالت | تجسم | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | استادان معماری در دانشگاه‌ها | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | مهندسان زیست‌پزشکی و بیوالکتریک | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | استادان شیمی در دانشگاه‌ها | استادان علوم کامپیوتر در دانشگاه‌ها | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | استادان علوم محیط‌زیست در دانشگاه‌ها | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان مواد و متالورژی | دانشمندان علوم مواد | استادان علوم ریاضی در دانشگاه‌ها | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی فناوری نانو | استادان فیزیک در دانشگاه‌ها</t>
+          <t>مدیران فنی و مهندسی و معماری | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | مهندسان پزشکی و بیوانجینیرینگ | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | استراتژی‌های یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال | نظارت | مهارت‌های علمی | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | تولید و صنایع غذایی | ارتباطات و رسانه | ریاضیات | جغرافیا | رایانه و الکترونیک | امور دفتری و اداری | حقوق و مقررات دولتی | منابع انسانی و امور پرسنلی</t>
+          <t>زیست‌شناسی | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | تولید مواد غذایی | ارتباطات و رسانه | ریاضیات | جغرافیا | رایانه و الکترونیک | اداری | قانون و دولت | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | روانی ایده‌ها | دید نزدیک | مرتب‌سازی اطلاعات | ابتکار | انعطاف‌پذیری در دسته‌بندی | محاسبات عددی | استدلال ریاضی | حافظه و به‌خاطرسپاری</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | روانی ایده‌ها | بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | استادان علوم زیستی در دانشگاه‌ها | زیست‌شناسان | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | استادان شیمی در دانشگاه‌ها | استادان اقتصاد در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان علوم خانواده و مدیریت مصرف در دانشگاه‌ها | مروجان کشاورزی و اقتصاد خانواده | مدیران مزارع، دامداری‌ها و واحدهای کشاورزی | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | مدیران علوم طبیعی | استادان علوم ورزشی و تربیت بدنی در دانشگاه‌ها | متخصصان علوم خاک و گیاه‌پزشکی</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان ترویج و آموزش کشاورزی و اقتصاد خانواده | مدیران امور کشاورزی، دامپروری و شیلات | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مدیران علوم طبیعی و پایه‌ای | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | استراتژی‌های یادگیری | یادگیری فعال | مهارت‌های علمی | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | ریاضیات</t>
+          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | علوم | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی | آموزش و تدریس | رایانه و الکترونیک | امور دفتری و اداری | پزشکی و دندانپزشکی | ارتباطات و رسانه | جغرافیا</t>
+          <t>زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی | آموزش و پرورش | رایانه و الکترونیک | اداری | پزشکی و دندان‌پزشکی | ارتباطات و رسانه | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | روانی ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی | ابتکار | دید دور</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | اصالت | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی در دانشگاه‌ها | استادان مردم‌شناسی و باستان‌شناسی در دانشگاه‌ها | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | بیوشیمی‌دانان و بیوفیزیک‌دانان | دانشمندان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | زیست‌شناسان | استادان شیمی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | متخصصان ژنتیک | استادان جغرافیا در دانشگاه‌ها | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | زیست‌شناسان سلولی و مولکولی | استادان فیزیک در دانشگاه‌ها | استادان روان‌شناسی در دانشگاه‌ها | استادان علوم ورزشی و تربیت بدنی در دانشگاه‌ها | دستیاران آموزشی در دانشگاه‌ها | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | زیست‌شناسان | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | متخصصان ژنتیک | استادان جغرافیای دانشگاه | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان سلولی و مولکولی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | استادان روان‌شناسی دانشگاه | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | درک مطلب | نگارش | سخن گفتن | شنیدن فعال | یادگیری فعال | تفکر انتقادی | نظارت | مهارت‌های علمی | ریاضیات</t>
+          <t>راهبردهای یادگیری | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | ریاضیات | زیست‌شناسی | رایانه و الکترونیک | جغرافیا | منابع انسانی و امور پرسنلی | امور دفتری و اداری | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ریاضیات | زیست‌شناسی | رایانه و الکترونیک | جغرافیا | پرسنل و منابع انسانی | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | استدلال ریاضی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | روانی ایده‌ها | ابتکار</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی در دانشگاه‌ها | استادان مردم‌شناسی و باستان‌شناسی در دانشگاه‌ها | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | استادان علوم زیستی در دانشگاه‌ها | زیست‌شناسان | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | استادان شیمی در دانشگاه‌ها | کارشناسان حفاظت از منابع طبیعی و جنگل‌داری | استادان اقتصاد در دانشگاه‌ها | استادان علوم تربیتی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان علوم خانواده و مدیریت مصرف در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | کارشناسان برنامه‌ریزی آموزشی | استادان علوم ریاضی در دانشگاه‌ها | مدیران علوم طبیعی | استادان علوم ورزشی و تربیت بدنی در دانشگاه‌ها | دستیاران آموزشی در دانشگاه‌ها</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | دانشمندان حفاظت از منابع طبیعی | استادان اقتصاد دانشگاه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان جغرافیای دانشگاه | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | مدیران علوم طبیعی و پایه‌ای | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | مهارت‌های علمی | نگارش | شنیدن فعال | یادگیری فعال | استراتژی‌های یادگیری | نظارت | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | ریاضیات | فیزیک | شیمی | رایانه و الکترونیک | زیست‌شناسی | جغرافیا | خدمات مشتریان و خدمات فردی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ریاضیات | فیزیک | شیمی | رایانه و الکترونیک | زیست‌شناسی | جغرافیا | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | استدلال ریاضی | مرتب‌سازی اطلاعات | محاسبات عددی | انعطاف‌پذیری در دسته‌بندی | ابتکار | روانی ایده‌ها | حافظه و به‌خاطرسپاری</t>
+          <t>بیان شفاهی | وضوح گفتار | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال ریاضی | ترتیب‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | حفظ کردن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی در دانشگاه‌ها | استادان مردم‌شناسی و باستان‌شناسی در دانشگاه‌ها | استادان علوم زیستی در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان شیمی در دانشگاه‌ها | استادان علوم کامپیوتر در دانشگاه‌ها | استادان مهندسی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | مدیران علوم طبیعی | استادان فیزیک در دانشگاه‌ها | استادان روان‌شناسی در دانشگاه‌ها | استادان علوم ورزشی و تربیت بدنی در دانشگاه‌ها | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی و حرفه‌ای | استادان جامعه‌شناسی در دانشگاه‌ها | دستیاران آموزشی در دانشگاه‌ها | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | مدیران علوم طبیعی و پایه‌ای | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | استادان روان‌شناسی دانشگاه | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان جامعه‌شناسی دانشگاه | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | نظارت | استراتژی‌های یادگیری | یادگیری فعال | تفکر انتقادی | مهارت‌های علمی | شنیدن فعال | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | زبان انگلیسی | ریاضیات | آموزش و تدریس | زیست‌شناسی | فیزیک | مهندسی و فناوری | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>شیمی | زبان انگلیسی | ریاضیات | آموزش و پرورش | زیست‌شناسی | فیزیک | مهندسی و فناوری | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | درک شفاهی | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | روانی ایده‌ها | انعطاف‌پذیری در ادراک الگوها | حافظه و به‌خاطرسپاری | استدلال ریاضی | ابتکار</t>
+          <t>بیان شفاهی | بیان کتبی | درک شفاهی | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها | انعطاف‌پذیری بستار | حفظ کردن | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی در دانشگاه‌ها | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیست‌پزشکی و بیوالکتریک | استادان علوم زیستی در دانشگاه‌ها | تکنسین‌های زیست‌شناسی | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | تکنسین‌های شیمی | شیمیدانان | استادان مهندسی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | زیست‌شناسان سلولی و مولکولی | مدیران علوم طبیعی | استادان فیزیک در دانشگاه‌ها | استادان علوم ورزشی و تربیت بدنی در دانشگاه‌ها | دستیاران آموزشی در دانشگاه‌ها | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های علوم زیستی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | تکنسین‌های شیمی | شیمی‌دانان | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان سلولی و مولکولی | مدیران علوم طبیعی و پایه‌ای | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | مهارت‌های علمی | نگارش | شنیدن فعال | استراتژی‌های یادگیری | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | زیست‌شناسی | شیمی | ریاضیات | رایانه و الکترونیک | جغرافیا | مهندسی و فناوری | فیزیک | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | زبان انگلیسی | زیست‌شناسی | شیمی | ریاضیات | رایانه و الکترونیک | جغرافیا | مهندسی و فناوری | فیزیک | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | ابتکار | روانی ایده‌ها | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک کتبی | وضوح گفتار | درک شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی در دانشگاه‌ها | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | استادان علوم زیستی در دانشگاه‌ها | زیست‌شناسان | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | استادان شیمی در دانشگاه‌ها | کارشناسان حفاظت از منابع طبیعی و جنگل‌داری | استادان اقتصاد در دانشگاه‌ها | استادان مهندسی در دانشگاه‌ها | کارشناسان و متخصصان علوم محیط‌زیست و بهداشت محیط | استادان علوم خانواده و مدیریت مصرف در دانشگاه‌ها | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | مدیران علوم طبیعی | استادان فیزیک در دانشگاه‌ها | استادان علوم ورزشی و تربیت بدنی در دانشگاه‌ها | دستیاران آموزشی در دانشگاه‌ها</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | دانشمندان حفاظت از منابع طبیعی | استادان اقتصاد دانشگاه | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | مدیران علوم طبیعی و پایه‌ای | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | مهارت‌های علمی | استراتژی‌های یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | سخن گفتن | علوم | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک | شیمی | مهندسی و فناوری</t>
+          <t>ریاضیات | فیزیک | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | شیمی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | وضوح گفتار | دید نزدیک | تشخیص گفتار | محاسبات عددی | روانی ایده‌ها | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | ابتکار</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | توانایی عددی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اخترشناسان | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیست‌پزشکی و بیوالکتریک | استادان علوم زیستی در دانشگاه‌ها | دبیران آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | استادان شیمی در دانشگاه‌ها | استادان علوم کامپیوتر در دانشگاه‌ها | دانشمندان و محققان علوم کامپیوتر و داده | استادان مهندسی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | ریاضیدانان | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم | کارشناسان و تکنسین‌های مهندسی فناوری نانو | فیزیکدانان | دستیاران آموزشی در دانشگاه‌ها | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>ستاره‌شناسان و اخترشناسان | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | پژوهشگران علوم رایانه و اطلاعات | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | ریاضی‌دانان | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | فیزیک‌دانان | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
